--- a/dataset/stats/Ground/Sweden_Arcade.xlsx
+++ b/dataset/stats/Ground/Sweden_Arcade.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Rank_Info</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Сыграно игр</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Победы</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Процент побед</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Возрождения</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Наземные убийства</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Воздушные убийства</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Морские убийства</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Смерти</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Убийств за возрождение</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Убийств за смерть</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SL за игру</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RP за игру</t>
         </is>
@@ -491,70 +508,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>sw_strv_m31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Strvm/31</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>165,429</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>88,196</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>53.3%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>185,986</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>237,854</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>14,600</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>138,656</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>1.82</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>379</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
@@ -563,70 +585,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>sw_sav_fm48</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>SAV20.12.48</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>164,965</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>92,062</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>55.8%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>216,114</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>484,617</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>13,032</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>189,841</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2.30</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2.62</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>10,433</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>899</t>
         </is>
@@ -635,70 +662,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>sw_strv_m38</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Strvm/38</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>152,680</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>76,715</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>50.2%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>172,057</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>139,948</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>13,004</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>138,089</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>271</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>136</t>
         </is>
@@ -707,70 +739,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>sw_bt_42</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>BT-42</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>146,032</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>69,645</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>167,443</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>172,056</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>8,924</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>144,194</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>433</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>132</t>
         </is>
@@ -779,70 +816,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>sw_t_34_1941</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>▄T-34</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>144,806</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>73,277</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>50.6%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>158,124</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>201,578</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>11,270</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>128,857</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1.65</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2,528</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>251</t>
         </is>
@@ -851,70 +893,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>sw_m24_chaffee_dk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>M24DK</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.3#6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>119,633</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>62,079</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>51.9%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>132,400</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>170,427</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>13,753</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>107,438</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2,615</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>273</t>
         </is>
@@ -923,70 +970,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>sw_pvkv_II</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>PvkvII</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>111,614</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>59,612</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>123,440</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>219,521</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>9,207</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>97,008</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2.36</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>3,913</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>348</t>
         </is>
@@ -995,70 +1047,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>sw_pzkpfw_IV_ausf_J</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>▄Pz.IV</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#8</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>103,815</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>51,355</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>49.5%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>111,625</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>126,144</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>10,468</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>89,341</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2,412</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>224</t>
         </is>
@@ -1067,70 +1124,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>sw_ikv_72</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Ikv72</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>93,174</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>44,285</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>103,121</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>89,720</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>6,256</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>88,818</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>298</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>119</t>
         </is>
@@ -1139,70 +1201,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>sw_stormpjas_fm43_44</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Spjfm/43-44</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>85,230</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>40,460</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>93,595</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>98,066</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>6,617</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>77,018</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>880</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>147</t>
         </is>
@@ -1211,70 +1278,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>sw_t_28</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>▄T-28</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>81,078</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>43,965</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>54.2%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>93,104</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>222,175</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>6,430</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>70,340</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>852</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>367</t>
         </is>
@@ -1283,70 +1355,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>sw_strv_m40l</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Strvm/40L</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#12</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>80,048</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>37,567</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>46.9%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>86,224</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>58,836</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>6,561</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>71,949</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>574</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>141</t>
         </is>
@@ -1355,70 +1432,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>sw_strv_m42_eh</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Strvm/42EH</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#13</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>79,741</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>39,236</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>88,599</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>115,278</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>6,129</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>71,294</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>1,884</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>248</t>
         </is>
@@ -1427,70 +1509,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>sw_sherman_3_4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>ShermanIII/IV</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#14</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>77,178</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>44,821</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>58.1%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>88,387</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>205,344</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>8,252</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>67,582</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2.42</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>3.16</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>9,378</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>902</t>
         </is>
@@ -1499,70 +1586,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>sw_strv_m42_delat_torn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Strvm/42DT</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>70,869</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>33,205</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>46.9%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>79,230</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>74,951</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>4,852</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>68,786</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>2,465</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>208</t>
         </is>
@@ -1571,70 +1663,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>sw_l_62_anti_II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>L-62ANTIII</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#16</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>68,932</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>32,199</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>46.7%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>73,663</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>48,240</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>37,852</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>51,530</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2,113</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>161</t>
         </is>
@@ -1643,70 +1740,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>sw_pt_76b</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>▄PT-76</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>60,383</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>27,222</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>45.1%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>66,105</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>30,010</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>5,176</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>58,601</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0.53</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>0.60</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>1,667</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>138</t>
         </is>
@@ -1715,70 +1817,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>sw_tgdgb_m40_lv</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Lvtdgbm/40</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.0#18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>59,142</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>27,503</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>46.5%</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>64,849</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>54,583</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>25,030</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>50,052</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>1,289</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>149</t>
         </is>
@@ -1787,70 +1894,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>sw_sav_m43_1944</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Savm/43(1944)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>58,329</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>28,349</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>48.6%</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>62,108</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>71,388</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>4,485</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>47,353</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>164</t>
         </is>
@@ -1859,70 +1971,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>sw_lago_1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>LagoI</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>56,500</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>25,989</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>46.0%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>60,643</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>33,026</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>3,941</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>51,447</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>916</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>138</t>
         </is>
@@ -1931,70 +2048,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>sw_t_34_85_zis_53</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>▄T-34-85</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>55,802</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>27,015</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>48.4%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>62,862</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>65,230</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>4,082</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>53,245</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>4,072</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>283</t>
         </is>
@@ -2003,70 +2125,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>sw_bkan_1c</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>Bkan1C</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>55,204</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>24,850</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>45.0%</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>62,137</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>48,200</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>20,858</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>47,846</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>3,715</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>243</t>
         </is>
@@ -2075,70 +2202,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>sw_sav_m43_1946</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>Savm/43(1946)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.0#23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>55,017</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>24,909</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>45.3%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>58,731</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>36,285</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>4,110</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>48,583</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>0.69</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>1,157</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>123</t>
         </is>
@@ -2147,70 +2279,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>sw_pvkv_iv</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>PvkvIV</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.0#24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>53,927</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>25,712</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>59,303</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>46,380</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>3,418</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>51,869</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>1,765</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>170</t>
         </is>
@@ -2219,70 +2356,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>sw_pbv_301</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Pbv301</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>51,671</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>23,151</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>44.8%</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>56,088</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>24,887</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>34,295</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>37,976</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>847</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>120</t>
         </is>
@@ -2291,70 +2433,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>sw_pvkv_III</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>PvkvIII</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.3#26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>50,975</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>24,269</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>47.6%</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>54,922</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>54,736</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>3,526</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>45,281</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>1,881</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>179</t>
         </is>
@@ -2363,70 +2510,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>sw_pvkv_m43_1946</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Pvkvm/43(1946)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>49,644</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>23,846</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>48.0%</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>53,685</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>44,788</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>4,058</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>46,023</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>2,189</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>180</t>
         </is>
@@ -2435,70 +2587,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>sw_strv_74</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Strv74</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.7#28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>49,361</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>23,543</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>54,833</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>40,451</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>4,291</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>47,826</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>3,321</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -2507,70 +2664,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>sw_strv121b_christian2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>ChristianII</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.7#29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>48,990</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>24,894</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>50.8%</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>62,122</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>87,365</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>1,680</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>51,464</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>20,193</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>1,550</t>
         </is>
@@ -2579,70 +2741,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>sw_pbv_501</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Pbv501</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>48,387</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>22,220</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>45.9%</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>55,256</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>30,139</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>2,445</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>49,478</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>0.59</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>3,030</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>219</t>
         </is>
@@ -2651,70 +2818,75 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>sw_lvkv_42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Lvkv42</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.7#31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>42,424</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>19,200</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>45.3%</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>46,144</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>29,140</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>30,718</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>31,931</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>2,766</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>181</t>
         </is>
@@ -2723,70 +2895,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>sw_pvlvv_fm42</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Pvlvvfm/42</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#32</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>39,910</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>18,879</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>47.3%</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>42,883</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>23,710</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>15,781</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>31,535</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>485</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>107</t>
         </is>
@@ -2795,70 +2972,75 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>sw_a_34_comet</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>▄CometI</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#33</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>38,840</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>18,227</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>46.9%</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>42,473</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>28,275</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>2,878</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>36,067</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>2,573</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>203</t>
         </is>
@@ -2867,70 +3049,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>sw_pvkv_m43_1963</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Pvkvm/43(1963)</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.7#34</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>38,703</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>17,716</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>45.8%</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>42,090</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>32,541</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>3,912</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>35,902</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>2,338</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>171</t>
         </is>
@@ -2939,70 +3126,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>sw_t_55m</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>▄T-55M</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#35</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>38,415</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>18,641</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>48.5%</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>42,719</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>47,215</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>1,802</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>34,794</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>5,354</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>411</t>
         </is>
@@ -3011,70 +3203,75 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>sw_strv_m41_s2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Strvm/41S-II</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>38,357</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>17,903</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>46.7%</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>41,139</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>25,003</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>3,130</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>34,837</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>946</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>141</t>
         </is>
@@ -3083,70 +3280,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>sw_t_54_1951</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>▄T-54</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>38,297</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>18,133</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>47.3%</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>43,190</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>39,142</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>2,233</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>35,557</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>4,666</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>331</t>
         </is>
@@ -3155,70 +3357,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>sw_ikv_103</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Ikv103</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#38</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>38,088</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>17,617</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>46.3%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>42,136</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>26,185</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>2,577</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>36,350</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>2,075</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>157</t>
         </is>
@@ -3227,70 +3434,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>sw_zsu_57_2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>▄ZSU-57-2</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.0#39</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>37,790</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>17,314</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>45.8%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>43,173</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>32,428</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>7,980</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>37,045</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>4,233</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>245</t>
         </is>
@@ -3299,70 +3511,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>sw_ikv_91</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Ikv91</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#40</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>37,473</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>17,841</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>47.6%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>41,571</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>31,336</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>1,902</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>36,234</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>3,516</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>274</t>
         </is>
@@ -3371,70 +3588,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>sw_t_72m1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>▄T-72M1</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#41</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>37,174</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>17,724</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>41,896</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>49,314</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>1,092</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>34,615</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>6,279</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>459</t>
         </is>
@@ -3443,70 +3665,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>sw_charioteer_mk_7</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>▄CharioteerMkVII</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#42</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>37,039</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>17,169</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>46.4%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>42,496</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>27,074</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1,899</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>38,475</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>0.75</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>3,336</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>238</t>
         </is>
@@ -3515,70 +3742,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>sw_strv_122b_plus</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Strv122B+</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>36,331</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>19,286</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>53.1%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>39,910</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>65,696</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1,093</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>31,034</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>8,956</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>814</t>
         </is>
@@ -3587,70 +3819,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>sw_strv_m39</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Strvm/39</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#44</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>33,926</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>20,766</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>61.2%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>37,743</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>52,149</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1,805</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>26,292</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>1,036</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>190</t>
         </is>
@@ -3659,70 +3896,75 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>sw_itpsv_90</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>ItPsVLeopard</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#45</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>33,911</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>15,119</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>44.6%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>37,466</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>22,087</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>18,504</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>28,407</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>4,168</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>272</t>
         </is>
@@ -3731,70 +3973,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>sw_strv_121</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Strv121</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.7#46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>32,971</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>15,862</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>48.1%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>36,765</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>39,688</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>946</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>29,525</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>6,255</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>523</t>
         </is>
@@ -3803,70 +4050,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>sw_cv_90105</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>CV90105TML</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#47</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>32,462</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>15,941</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>49.1%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>36,762</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>33,227</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1,184</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>31,923</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>4,302</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>334</t>
         </is>
@@ -3875,70 +4127,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>sw_strv_122b_plss</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Strv122BPLSS</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#48</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>30,108</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>15,930</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>52.9%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>32,184</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>56,741</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>875</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>24,158</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>1.79</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>2.38</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>9,245</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>845</t>
         </is>
@@ -3947,70 +4204,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>sw_strv_104</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Strv104</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#49</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>29,469</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>14,418</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>48.9%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>32,131</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>34,099</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1,515</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>26,212</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>5,041</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>371</t>
         </is>
@@ -4019,70 +4281,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>sw_strv_101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Strv101</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#50</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>29,393</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>13,973</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>31,850</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>29,179</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1,680</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>25,606</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>4,449</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>313</t>
         </is>
@@ -4091,70 +4358,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>sw_cv_90105_tml</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>CV90105</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.3#51</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>27,213</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>13,425</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>49.3%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>32,014</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>36,344</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>973</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>27,274</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>13,839</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>1,099</t>
         </is>
@@ -4163,70 +4435,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>sw_strv_122</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Strv122A</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#52</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>26,965</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>13,276</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>28,943</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>41,992</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>844</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>21,746</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>8,023</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>718</t>
         </is>
@@ -4235,70 +4512,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>sw_strv_81</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Strv81</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#53</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>25,504</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>11,893</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>46.6%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>28,236</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>20,630</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1,466</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>23,700</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>3,931</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>274</t>
         </is>
@@ -4307,70 +4589,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>sw_strv_103a</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Strv103A</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#54</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>25,390</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>12,375</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>48.7%</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>28,081</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>35,250</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>1,446</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>20,704</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>1.77</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>6,021</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>433</t>
         </is>
@@ -4379,70 +4666,75 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>sw_strv_105</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Strv105</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#55</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>24,336</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>11,561</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>47.5%</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>26,955</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>26,917</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>760</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>22,550</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>5,068</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>365</t>
         </is>
@@ -4451,70 +4743,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>sw_leopard_2a4_fin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>▄Leopard2A4</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.7#56</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>23,519</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>11,123</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>47.3%</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>26,147</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>23,698</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>21,652</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>5,617</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>469</t>
         </is>
@@ -4523,70 +4820,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>sw_landsverk_ush_204_gk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>U-SH204GK</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Ранг 4БР 5.0#57</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>23,336</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>10,144</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>43.5%</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>24,824</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>5,098</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>20,555</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>16,472</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>1.56</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>2,678</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>159</t>
         </is>
@@ -4595,70 +4897,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>sw_ikv_73</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Ikv73</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#58</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>21,451</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>13,423</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>62.6%</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>27,002</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>98,983</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>2,154</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>21,285</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>4.75</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>13,331</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>1,350</t>
         </is>
@@ -4667,70 +4974,75 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>sw_landsverk_ush_405</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>U-SH405</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#59</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>21,040</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>10,299</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>48.9%</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>23,105</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>19,697</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>701</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>20,567</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>3,532</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>293</t>
         </is>
@@ -4739,70 +5051,75 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>sw_vickers_mk_e_37</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>VickersMk.E</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#60</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>20,683</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>9,865</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>21,840</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>16,777</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>2,090</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>17,612</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>136</t>
         </is>
@@ -4811,70 +5128,75 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>sw_ikv_91_105</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Ikv91-105</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#61</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>19,870</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>9,980</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>50.2%</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>21,620</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>21,583</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>18,443</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>4,389</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>359</t>
         </is>
@@ -4883,70 +5205,75 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>sw_cv_9030_fin</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>CV9030FIN</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#62</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>18,149</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>8,685</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>20,123</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>14,545</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>1,748</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>17,248</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>4,175</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>334</t>
         </is>
@@ -4955,70 +5282,75 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>sw_veak_40</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>VEAK40</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#63</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>17,557</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>7,773</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>44.3%</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>18,734</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>6,321</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>10,912</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>13,262</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>2,913</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>179</t>
         </is>
@@ -5027,70 +5359,75 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>sw_strf_9056</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Strf9040BILL</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.7#64</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>16,416</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>7,496</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>45.7%</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>18,930</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>11,552</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>3,986</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>15,428</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>4,552</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>384</t>
         </is>
@@ -5099,70 +5436,75 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>sw_leopard_2a6nl</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>▄Leopard2A6</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#65</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>15,770</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>7,740</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>49.1%</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>17,042</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>21,499</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>459</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>13,771</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>7,051</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>595</t>
         </is>
@@ -5171,70 +5513,75 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>sw_strv_103_0</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Strv103-0</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#66</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>15,320</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>8,006</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>19,078</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>30,541</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>14,600</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>2.14</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>18,859</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>1,282</t>
         </is>
@@ -5243,70 +5590,75 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>sw_pvrbv_551</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>Pvrbv551</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#67</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>14,788</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>6,679</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>45.2%</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>16,450</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>9,528</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>1,003</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>14,139</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>3,175</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>188</t>
         </is>
@@ -5315,70 +5667,75 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>sw_t_80u</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>T80U</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Ранг 8БР 11.3#68</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>14,779</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>7,085</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>18,445</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>20,382</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>429</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>15,704</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>7,124</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>627</t>
         </is>
@@ -5387,70 +5744,75 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>sw_strv_103c</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>Strv103C</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#69</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>14,686</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>7,220</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>16,386</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>22,447</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>674</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>12,086</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>6,664</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>484</t>
         </is>
@@ -5459,70 +5821,75 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>sw_cv_90_mk4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>CV90Mk.IV</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Ранг 8БР 10.7#70</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>14,624</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>6,982</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>17,884</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>13,089</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>1,754</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>15,306</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>5,798</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>543</t>
         </is>
@@ -5531,70 +5898,75 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>sw_leopard_1a5no</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>Leopard1A5NO2</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#71</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>13,366</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>6,555</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>16,334</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>20,802</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>555</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>13,977</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>15,855</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>1,108</t>
         </is>
@@ -5603,70 +5975,75 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>sw_kv_1_1942_fin</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>▄KV-1m1942</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.7#72</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>12,961</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>7,320</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>56.5%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>16,767</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>43,067</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>1,380</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>12,268</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>2.65</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>3.62</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>20,059</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>1,339</t>
         </is>
@@ -5675,70 +6052,75 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>sw_strf_90c</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>Strf9040C</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.3#73</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>12,872</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>6,053</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>47.0%</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>14,195</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>12,523</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>3,793</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>11,283</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>5,729</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>503</t>
         </is>
@@ -5747,70 +6129,75 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>sw_cv_90120</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>CV90120-T</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#74</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>12,587</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>6,265</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>49.8%</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>14,337</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>13,911</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>324</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>12,198</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>5,183</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>522</t>
         </is>
@@ -5819,70 +6206,75 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>sw_k9_vidar</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>VIDAR</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#75</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>12,201</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>5,768</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>47.3%</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>14,651</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>14,724</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1,849</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>11,996</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>1.13</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>12,003</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>721</t>
         </is>
@@ -5891,70 +6283,75 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>sw_strf_90b</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>Strf9040B</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.7#76</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>11,955</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>5,928</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>49.6%</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>13,946</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>13,781</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>5,498</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>11,354</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>5,940</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>478</t>
         </is>
@@ -5963,70 +6360,75 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>sw_lvkv_90c</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Lvkv9040C</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.3#77</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>9,966</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>4,356</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>43.7%</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>10,805</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>5,998</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>7,384</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>7,571</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>1.77</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>5,535</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>386</t>
         </is>
@@ -6035,70 +6437,75 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>sw_udes_33</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>UDES33</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#78</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>7,666</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>3,504</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>45.7%</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>8,637</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>5,408</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>371</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>7,485</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0.67</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>3,407</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>216</t>
         </is>
@@ -6107,70 +6514,75 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>sw_crotale_ng</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>ItO90M</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#79</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>6,738</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>3,044</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>45.2%</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>7,343</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>2,798</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>13,647</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>4,188</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>2.24</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>3.93</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>5,431</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>346</t>
         </is>
@@ -6179,70 +6591,75 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>sw_kungstiger</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>Kungstiger</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#80</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>6,539</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>3,530</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>54.0%</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>8,612</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>18,731</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>6,849</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>2.25</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>2.82</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>23,367</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>1,328</t>
         </is>
@@ -6251,70 +6668,75 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>sw_bmp_2md</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>BMP-2MD</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#81</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>6,238</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>2,994</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>48.0%</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>7,128</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>4,160</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>1,287</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>5,986</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>3,784</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>302</t>
         </is>
@@ -6323,70 +6745,75 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>sw_strv_m41_s1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>Strvm/41S-I</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#82</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>5,817</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>2,867</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>49.3%</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>6,640</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>5,648</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>596</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>5,257</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>3,041</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>420</t>
         </is>
@@ -6395,70 +6822,75 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>sw_lvrbv_701</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Lvrbv701</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#83</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>5,629</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>2,437</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>43.3%</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>6,048</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>1,410</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>6,677</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>3,919</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>2.06</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>3,253</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>207</t>
         </is>
@@ -6467,70 +6899,75 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>sw_pbv_302_bill</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>Pbv302(BILL)</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#84</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>5,411</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>2,440</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>45.1%</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>5,966</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>3,506</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>387</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>5,061</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>4,190</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>279</t>
         </is>
@@ -6539,70 +6976,75 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>sw_patria_amv_ctcv_105</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>CT-CV105HP</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#85</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>4,943</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>2,547</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>51.5%</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>5,751</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>4,861</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>6,710</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>677</t>
         </is>
@@ -6611,70 +7053,75 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>sw_cv_9035_dk</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>CV9035DK</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.7#86</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>4,750</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>2,414</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>50.8%</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>5,564</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>6,179</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>381</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>4,721</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>15,106</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>1,131</t>
         </is>
@@ -6683,70 +7130,75 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>sw_pbil_m40</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>Pbilm/40</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Ранг 1БР 2.0#87</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>4,632</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>2,807</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>60.6%</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>5,094</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>10,365</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>590</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>4,094</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>2.68</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>3,237</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>667</t>
         </is>
@@ -6755,70 +7207,75 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>sw_asrad_r</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>ASRAD-R</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.3#88</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>4,549</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>1,987</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>43.7%</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>4,831</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>1,322</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>7,609</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>2,889</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>3.09</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>4,259</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>314</t>
         </is>
@@ -6827,70 +7284,75 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>sw_eldenhet_98</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>EldE98</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#89</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>2,903</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>1,263</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>43.5%</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>3,264</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>3,521</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>2,236</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>3,743</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>241</t>
         </is>
@@ -6899,70 +7361,75 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>sw_strv_81_rb52</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>Strv81(RB52)</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#90</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>2,380</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>1,082</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>45.5%</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>2,869</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>2,563</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>139</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>2,325</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>11,386</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>793</t>
         </is>
@@ -6971,70 +7438,75 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>sw_nasams_fcs</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>NASAMS3(TADS)</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#91</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>1,905</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>919</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>48.2%</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>2,100</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>664</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>4,011</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>1,549</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>2.23</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>3.02</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>5,518</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>343</t>
         </is>
@@ -7043,70 +7515,75 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>sw_vickers_mk_e_45</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>▄T-26E</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#92</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>1,854</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>1,004</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>54.2%</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>2,204</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>3,702</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>183</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t>1,686</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>2.30</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>2,396</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>506</t>
         </is>
@@ -7115,70 +7592,75 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>sw_strv_m39_td</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>Strvm/39TD</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#93</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>639</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>344</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>53.8%</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>817</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>577</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>691</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>240</t>
         </is>
